--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/4_fold/61.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/4_fold/61.xlsx
@@ -426,13 +426,13 @@
         <v>-17.77333271878869</v>
       </c>
       <c r="E2">
-        <v>-16.83881115257528</v>
+        <v>-18.25520461032438</v>
       </c>
       <c r="F2">
-        <v>3.020950568102134</v>
+        <v>2.723949376237205</v>
       </c>
       <c r="G2">
-        <v>-10.61924263053545</v>
+        <v>-11.62249909088659</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-17.00754690530196</v>
       </c>
       <c r="E3">
-        <v>-16.91565935648545</v>
+        <v>-18.63260310564962</v>
       </c>
       <c r="F3">
-        <v>3.310521304363951</v>
+        <v>3.256210223966804</v>
       </c>
       <c r="G3">
-        <v>-10.87891522352835</v>
+        <v>-11.63754349173664</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-16.16025658507686</v>
       </c>
       <c r="E4">
-        <v>-17.00800852692387</v>
+        <v>-18.51311026200922</v>
       </c>
       <c r="F4">
-        <v>3.454155241804969</v>
+        <v>3.160621595888158</v>
       </c>
       <c r="G4">
-        <v>-10.65820713655386</v>
+        <v>-11.87716125855821</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-15.29563354094417</v>
       </c>
       <c r="E5">
-        <v>-17.69213868068465</v>
+        <v>-19.9814498451003</v>
       </c>
       <c r="F5">
-        <v>3.45385371607035</v>
+        <v>3.101249190659907</v>
       </c>
       <c r="G5">
-        <v>-10.52216769069928</v>
+        <v>-11.2872665278228</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-14.41546287776388</v>
       </c>
       <c r="E6">
-        <v>-18.81581157857794</v>
+        <v>-19.70476914017966</v>
       </c>
       <c r="F6">
-        <v>3.571057763157646</v>
+        <v>3.225711392930532</v>
       </c>
       <c r="G6">
-        <v>-10.41842858987587</v>
+        <v>-12.28991268096388</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-13.55278754128314</v>
       </c>
       <c r="E7">
-        <v>-19.2666121090935</v>
+        <v>-20.66776725180679</v>
       </c>
       <c r="F7">
-        <v>3.042454985878809</v>
+        <v>3.36983075366959</v>
       </c>
       <c r="G7">
-        <v>-10.0108877473066</v>
+        <v>-10.24557711934589</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-12.72458142561378</v>
       </c>
       <c r="E8">
-        <v>-19.62387700898064</v>
+        <v>-22.0846407278007</v>
       </c>
       <c r="F8">
-        <v>3.528335542725665</v>
+        <v>3.039237606886335</v>
       </c>
       <c r="G8">
-        <v>-10.09403062040137</v>
+        <v>-11.35810482006965</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-11.94778461125062</v>
       </c>
       <c r="E9">
-        <v>-20.42514519989784</v>
+        <v>-22.30431247343878</v>
       </c>
       <c r="F9">
-        <v>3.304124651279534</v>
+        <v>3.515055156523983</v>
       </c>
       <c r="G9">
-        <v>-8.794437197352105</v>
+        <v>-10.45512249057515</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-11.23060558284282</v>
       </c>
       <c r="E10">
-        <v>-21.16182829451763</v>
+        <v>-22.5286077910387</v>
       </c>
       <c r="F10">
-        <v>3.445588266125216</v>
+        <v>3.802347882428102</v>
       </c>
       <c r="G10">
-        <v>-8.65229467939696</v>
+        <v>-10.91378476504057</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-10.58191926735824</v>
       </c>
       <c r="E11">
-        <v>-21.2769330468446</v>
+        <v>-23.31346479215209</v>
       </c>
       <c r="F11">
-        <v>3.511675417520561</v>
+        <v>3.519851403786192</v>
       </c>
       <c r="G11">
-        <v>-8.053504557013893</v>
+        <v>-11.02593691794239</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-10.00769526262986</v>
       </c>
       <c r="E12">
-        <v>-22.90924414527942</v>
+        <v>-25.50647342832062</v>
       </c>
       <c r="F12">
-        <v>3.399676831192457</v>
+        <v>3.723568485687063</v>
       </c>
       <c r="G12">
-        <v>-7.726937700088599</v>
+        <v>-9.307101816242866</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-9.505540185287657</v>
       </c>
       <c r="E13">
-        <v>-23.57134780146689</v>
+        <v>-25.86727506640775</v>
       </c>
       <c r="F13">
-        <v>3.967285772734317</v>
+        <v>3.129494862360564</v>
       </c>
       <c r="G13">
-        <v>-7.088730263111923</v>
+        <v>-8.398922031798199</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-9.091607663596889</v>
       </c>
       <c r="E14">
-        <v>-24.5182698303668</v>
+        <v>-26.12177530563882</v>
       </c>
       <c r="F14">
-        <v>4.090739023508333</v>
+        <v>3.930070538796146</v>
       </c>
       <c r="G14">
-        <v>-6.891466504179666</v>
+        <v>-8.177268953014588</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-8.771609537028324</v>
       </c>
       <c r="E15">
-        <v>-24.51044462728154</v>
+        <v>-27.36691999031386</v>
       </c>
       <c r="F15">
-        <v>4.278937470485158</v>
+        <v>4.742659199307127</v>
       </c>
       <c r="G15">
-        <v>-6.166477319398797</v>
+        <v>-6.915248798042522</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-8.548762778674906</v>
       </c>
       <c r="E16">
-        <v>-25.83363756147877</v>
+        <v>-27.03192159712243</v>
       </c>
       <c r="F16">
-        <v>4.380188818129342</v>
+        <v>3.804309456437931</v>
       </c>
       <c r="G16">
-        <v>-5.660978888393863</v>
+        <v>-6.911544298901909</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-8.423693199812051</v>
       </c>
       <c r="E17">
-        <v>-26.1875332767042</v>
+        <v>-28.06420536106693</v>
       </c>
       <c r="F17">
-        <v>4.497599957067338</v>
+        <v>4.214227065713266</v>
       </c>
       <c r="G17">
-        <v>-5.734947466008425</v>
+        <v>-7.669230856522645</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-8.393870478072001</v>
       </c>
       <c r="E18">
-        <v>-28.16878141132606</v>
+        <v>-30.41356182658728</v>
       </c>
       <c r="F18">
-        <v>4.748706281347563</v>
+        <v>5.406325624877618</v>
       </c>
       <c r="G18">
-        <v>-5.303194489552011</v>
+        <v>-7.355027642433337</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-8.452064910250176</v>
       </c>
       <c r="E19">
-        <v>-28.16400839972197</v>
+        <v>-29.69026716537116</v>
       </c>
       <c r="F19">
-        <v>4.68771193274463</v>
+        <v>4.622264280984247</v>
       </c>
       <c r="G19">
-        <v>-4.764109474664601</v>
+        <v>-6.117544462282797</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-8.583830475041147</v>
       </c>
       <c r="E20">
-        <v>-29.23775034320668</v>
+        <v>-28.59913135322299</v>
       </c>
       <c r="F20">
-        <v>5.059731733341888</v>
+        <v>4.784057688629435</v>
       </c>
       <c r="G20">
-        <v>-3.826904004305085</v>
+        <v>-6.810128302942592</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-8.78630075577278</v>
       </c>
       <c r="E21">
-        <v>-29.7729457795662</v>
+        <v>-30.81808588121847</v>
       </c>
       <c r="F21">
-        <v>5.072443859505249</v>
+        <v>5.514966009754773</v>
       </c>
       <c r="G21">
-        <v>-3.964593904604064</v>
+        <v>-5.617236923784906</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-9.046837650608659</v>
       </c>
       <c r="E22">
-        <v>-30.79709187571891</v>
+        <v>-32.13028368052507</v>
       </c>
       <c r="F22">
-        <v>5.249977904538434</v>
+        <v>5.02468019505983</v>
       </c>
       <c r="G22">
-        <v>-3.285321979810937</v>
+        <v>-5.07723644808241</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-9.35174197040063</v>
       </c>
       <c r="E23">
-        <v>-30.87454010243509</v>
+        <v>-32.17589220649332</v>
       </c>
       <c r="F23">
-        <v>4.762008205101718</v>
+        <v>5.497953000036077</v>
       </c>
       <c r="G23">
-        <v>-3.358453845927841</v>
+        <v>-5.78307970506392</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-9.686921857346812</v>
       </c>
       <c r="E24">
-        <v>-32.1595195087186</v>
+        <v>-33.4149800571831</v>
       </c>
       <c r="F24">
-        <v>5.5293249303149</v>
+        <v>5.476914124739775</v>
       </c>
       <c r="G24">
-        <v>-2.561779813737783</v>
+        <v>-5.000623205890935</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-10.03878182181194</v>
       </c>
       <c r="E25">
-        <v>-32.09951949235396</v>
+        <v>-32.00263731943387</v>
       </c>
       <c r="F25">
-        <v>5.530509495700903</v>
+        <v>5.464036325095854</v>
       </c>
       <c r="G25">
-        <v>-2.558820151891164</v>
+        <v>-5.855571732976732</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-10.39105063366094</v>
       </c>
       <c r="E26">
-        <v>-32.4091425814434</v>
+        <v>-34.46754685620795</v>
       </c>
       <c r="F26">
-        <v>5.22254403289252</v>
+        <v>5.659653630532151</v>
       </c>
       <c r="G26">
-        <v>-1.933032138516987</v>
+        <v>-5.739452583209543</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-10.73038474478604</v>
       </c>
       <c r="E27">
-        <v>-32.37894898099727</v>
+        <v>-32.3428389292601</v>
       </c>
       <c r="F27">
-        <v>5.525913713350172</v>
+        <v>5.451155211982321</v>
       </c>
       <c r="G27">
-        <v>-2.256068401044319</v>
+        <v>-3.873326726928109</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-11.05121080350255</v>
       </c>
       <c r="E28">
-        <v>-31.69311159253559</v>
+        <v>-33.80964562389958</v>
       </c>
       <c r="F28">
-        <v>5.844556831980641</v>
+        <v>5.664766314142231</v>
       </c>
       <c r="G28">
-        <v>-1.981213595895873</v>
+        <v>-4.220325750504066</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-11.34437201413291</v>
       </c>
       <c r="E29">
-        <v>-33.03830385346208</v>
+        <v>-34.22040538723933</v>
       </c>
       <c r="F29">
-        <v>5.852053556975976</v>
+        <v>5.710972647870387</v>
       </c>
       <c r="G29">
-        <v>-1.39741209359635</v>
+        <v>-5.01560854475292</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-11.6017217111285</v>
       </c>
       <c r="E30">
-        <v>-31.90867601224871</v>
+        <v>-34.78327432825972</v>
       </c>
       <c r="F30">
-        <v>5.907718189709297</v>
+        <v>5.884238944044348</v>
       </c>
       <c r="G30">
-        <v>-2.500630968755972</v>
+        <v>-4.83094795783049</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-11.81657982079863</v>
       </c>
       <c r="E31">
-        <v>-31.80606984818292</v>
+        <v>-35.15192607603915</v>
       </c>
       <c r="F31">
-        <v>5.812714389017027</v>
+        <v>4.678730773363478</v>
       </c>
       <c r="G31">
-        <v>-1.98767432114642</v>
+        <v>-5.009846719694535</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-11.98368488531039</v>
       </c>
       <c r="E32">
-        <v>-32.83163562093703</v>
+        <v>-34.62740425291571</v>
       </c>
       <c r="F32">
-        <v>5.31131354051132</v>
+        <v>4.963554964407255</v>
       </c>
       <c r="G32">
-        <v>-1.931444027282216</v>
+        <v>-4.697858330157853</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-12.09427196835481</v>
       </c>
       <c r="E33">
-        <v>-32.35160152646494</v>
+        <v>-32.67178275270327</v>
       </c>
       <c r="F33">
-        <v>5.487492376473525</v>
+        <v>5.576422587368469</v>
       </c>
       <c r="G33">
-        <v>-1.975005524705404</v>
+        <v>-5.244847807781965</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-12.15051388167676</v>
       </c>
       <c r="E34">
-        <v>-32.06616728128747</v>
+        <v>-31.26392320422163</v>
       </c>
       <c r="F34">
-        <v>5.169094454594284</v>
+        <v>5.34177923685148</v>
       </c>
       <c r="G34">
-        <v>-2.311652294261313</v>
+        <v>-5.194038091933963</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-12.15672287288893</v>
       </c>
       <c r="E35">
-        <v>-31.99133198407372</v>
+        <v>-32.26497634717222</v>
       </c>
       <c r="F35">
-        <v>5.612542719600138</v>
+        <v>5.521299706916579</v>
       </c>
       <c r="G35">
-        <v>-3.217066008931369</v>
+        <v>-5.253352734064046</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-12.11646038529614</v>
       </c>
       <c r="E36">
-        <v>-30.36060132306757</v>
+        <v>-30.8053563407829</v>
       </c>
       <c r="F36">
-        <v>5.144410762725665</v>
+        <v>4.582880381185547</v>
       </c>
       <c r="G36">
-        <v>-2.369017890785085</v>
+        <v>-5.155162178897663</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-12.03518003056168</v>
       </c>
       <c r="E37">
-        <v>-29.67530735148682</v>
+        <v>-32.45285820527645</v>
       </c>
       <c r="F37">
-        <v>5.788425000032141</v>
+        <v>5.416691814556251</v>
       </c>
       <c r="G37">
-        <v>-2.887493553057622</v>
+        <v>-5.730567035226566</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-11.91944826998711</v>
       </c>
       <c r="E38">
-        <v>-29.75076984235064</v>
+        <v>-32.27203397391317</v>
       </c>
       <c r="F38">
-        <v>5.599351797077959</v>
+        <v>5.154728907094936</v>
       </c>
       <c r="G38">
-        <v>-3.687845834615818</v>
+        <v>-5.075900990907717</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-11.77632626376469</v>
       </c>
       <c r="E39">
-        <v>-30.95910029758031</v>
+        <v>-32.02354754816428</v>
       </c>
       <c r="F39">
-        <v>5.973208916574626</v>
+        <v>5.696280723614334</v>
       </c>
       <c r="G39">
-        <v>-3.448933530429529</v>
+        <v>-6.024735110473904</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-11.60637953633896</v>
       </c>
       <c r="E40">
-        <v>-28.61676975948286</v>
+        <v>-30.81305927506995</v>
       </c>
       <c r="F40">
-        <v>5.751663711430704</v>
+        <v>5.726628791783297</v>
       </c>
       <c r="G40">
-        <v>-3.658616712964285</v>
+        <v>-5.549624072330988</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-11.42533575866585</v>
       </c>
       <c r="E41">
-        <v>-29.89410510164142</v>
+        <v>-29.87837771141278</v>
       </c>
       <c r="F41">
-        <v>6.33403084662084</v>
+        <v>5.839570060215787</v>
       </c>
       <c r="G41">
-        <v>-3.560803498277238</v>
+        <v>-6.095737463798728</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-11.24159451893668</v>
       </c>
       <c r="E42">
-        <v>-28.11610620166883</v>
+        <v>-28.24901691379396</v>
       </c>
       <c r="F42">
-        <v>6.060792202072617</v>
+        <v>5.649421636372773</v>
       </c>
       <c r="G42">
-        <v>-3.728772511126772</v>
+        <v>-6.02027264915306</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-11.06158660588761</v>
       </c>
       <c r="E43">
-        <v>-27.4563890512834</v>
+        <v>-29.36812510988751</v>
       </c>
       <c r="F43">
-        <v>6.018227371447168</v>
+        <v>6.126299496286003</v>
       </c>
       <c r="G43">
-        <v>-4.424168358663009</v>
+        <v>-6.916771284846104</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-10.89004230833728</v>
       </c>
       <c r="E44">
-        <v>-27.22679994756852</v>
+        <v>-29.47387856338864</v>
       </c>
       <c r="F44">
-        <v>6.350536895489023</v>
+        <v>5.396232796441909</v>
       </c>
       <c r="G44">
-        <v>-4.197888757480583</v>
+        <v>-6.527910436614751</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-10.73005566572384</v>
       </c>
       <c r="E45">
-        <v>-27.2422556293567</v>
+        <v>-28.27936674659336</v>
       </c>
       <c r="F45">
-        <v>6.428363669716842</v>
+        <v>5.300925813280214</v>
       </c>
       <c r="G45">
-        <v>-5.012091075241194</v>
+        <v>-6.892874148228668</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-10.58098529734773</v>
       </c>
       <c r="E46">
-        <v>-26.35406790833628</v>
+        <v>-24.25323183211987</v>
       </c>
       <c r="F46">
-        <v>6.560648973739506</v>
+        <v>6.243024747014482</v>
       </c>
       <c r="G46">
-        <v>-4.913664272122531</v>
+        <v>-7.548229249075002</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-10.43922514440053</v>
       </c>
       <c r="E47">
-        <v>-26.02373384337276</v>
+        <v>-27.02990642618902</v>
       </c>
       <c r="F47">
-        <v>6.521843274387961</v>
+        <v>5.77589345796259</v>
       </c>
       <c r="G47">
-        <v>-4.583245261086449</v>
+        <v>-7.590258416029929</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-10.31055656635559</v>
       </c>
       <c r="E48">
-        <v>-24.28105024794899</v>
+        <v>-27.4714462273589</v>
       </c>
       <c r="F48">
-        <v>6.491763597257505</v>
+        <v>5.632925527913422</v>
       </c>
       <c r="G48">
-        <v>-5.609201212185825</v>
+        <v>-5.287989308845544</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-10.19263613393254</v>
       </c>
       <c r="E49">
-        <v>-24.37866150518433</v>
+        <v>-25.93882948420295</v>
       </c>
       <c r="F49">
-        <v>6.455018876004125</v>
+        <v>5.841094256236938</v>
       </c>
       <c r="G49">
-        <v>-4.401134183315707</v>
+        <v>-6.27997477313999</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-10.08205671906899</v>
       </c>
       <c r="E50">
-        <v>-24.12769347567924</v>
+        <v>-23.98994182483991</v>
       </c>
       <c r="F50">
-        <v>6.851331379055881</v>
+        <v>6.200158390654412</v>
       </c>
       <c r="G50">
-        <v>-5.249408705749594</v>
+        <v>-7.713284537179749</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-9.974238299530766</v>
       </c>
       <c r="E51">
-        <v>-22.68073281837836</v>
+        <v>-22.77623833520013</v>
       </c>
       <c r="F51">
-        <v>6.435398165701416</v>
+        <v>6.052926025215633</v>
       </c>
       <c r="G51">
-        <v>-5.506387415842185</v>
+        <v>-7.017242288996301</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-9.864418768582922</v>
       </c>
       <c r="E52">
-        <v>-21.8372683066577</v>
+        <v>-22.83929733575694</v>
       </c>
       <c r="F52">
-        <v>7.162916807414499</v>
+        <v>6.260486731865495</v>
       </c>
       <c r="G52">
-        <v>-5.339871984143485</v>
+        <v>-7.571831075752088</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-9.744148370274686</v>
       </c>
       <c r="E53">
-        <v>-21.04070520023448</v>
+        <v>-23.10371493306481</v>
       </c>
       <c r="F53">
-        <v>6.704443614456667</v>
+        <v>6.205579226938332</v>
       </c>
       <c r="G53">
-        <v>-5.700491358412696</v>
+        <v>-8.011846168095184</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-9.610854090621714</v>
       </c>
       <c r="E54">
-        <v>-20.39421572242545</v>
+        <v>-21.43410732270282</v>
       </c>
       <c r="F54">
-        <v>6.563047925738014</v>
+        <v>6.331602073395832</v>
       </c>
       <c r="G54">
-        <v>-5.501137461347073</v>
+        <v>-8.537465049702632</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-9.466458174672924</v>
       </c>
       <c r="E55">
-        <v>-20.05342993945222</v>
+        <v>-21.2538514148275</v>
       </c>
       <c r="F55">
-        <v>6.661822454847827</v>
+        <v>5.834207209650064</v>
       </c>
       <c r="G55">
-        <v>-5.268400416135659</v>
+        <v>-8.69288667130885</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-9.31032047675661</v>
       </c>
       <c r="E56">
-        <v>-20.22866376965304</v>
+        <v>-20.53392367403609</v>
       </c>
       <c r="F56">
-        <v>6.588571582153072</v>
+        <v>5.993667934688968</v>
       </c>
       <c r="G56">
-        <v>-5.550575626583226</v>
+        <v>-7.76297535647598</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-9.142956016614798</v>
       </c>
       <c r="E57">
-        <v>-19.29386446567167</v>
+        <v>-21.34926183369511</v>
       </c>
       <c r="F57">
-        <v>6.437129453573267</v>
+        <v>5.410237175753637</v>
       </c>
       <c r="G57">
-        <v>-6.387772745032427</v>
+        <v>-8.562034836739754</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-8.966411808878931</v>
       </c>
       <c r="E58">
-        <v>-18.58355067519853</v>
+        <v>-19.03615353836915</v>
       </c>
       <c r="F58">
-        <v>6.463330714523815</v>
+        <v>5.58632654803634</v>
       </c>
       <c r="G58">
-        <v>-5.834266761391257</v>
+        <v>-8.551164149713314</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-8.783807964913505</v>
       </c>
       <c r="E59">
-        <v>-17.73534485119184</v>
+        <v>-18.9755489707245</v>
       </c>
       <c r="F59">
-        <v>6.06739429027293</v>
+        <v>5.366906933648001</v>
       </c>
       <c r="G59">
-        <v>-6.759489210615681</v>
+        <v>-8.033869727202177</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-8.594254402303987</v>
       </c>
       <c r="E60">
-        <v>-17.56497007360126</v>
+        <v>-19.60161955923294</v>
       </c>
       <c r="F60">
-        <v>6.067170631074174</v>
+        <v>5.916386226212191</v>
       </c>
       <c r="G60">
-        <v>-7.100217819791539</v>
+        <v>-8.150566371963828</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-8.407613096397498</v>
       </c>
       <c r="E61">
-        <v>-17.46261750407989</v>
+        <v>-18.75286578987132</v>
       </c>
       <c r="F61">
-        <v>6.349791364826504</v>
+        <v>5.463030687068855</v>
       </c>
       <c r="G61">
-        <v>-6.5765479837904</v>
+        <v>-8.487925166598137</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-8.231193354861883</v>
       </c>
       <c r="E62">
-        <v>-16.55084549042752</v>
+        <v>-18.72412809381864</v>
       </c>
       <c r="F62">
-        <v>6.04851911063274</v>
+        <v>5.090981065245097</v>
       </c>
       <c r="G62">
-        <v>-6.73160210858196</v>
+        <v>-7.236621481239215</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-8.070418546318757</v>
       </c>
       <c r="E63">
-        <v>-16.27827663990584</v>
+        <v>-16.86663862535242</v>
       </c>
       <c r="F63">
-        <v>6.105346771199592</v>
+        <v>4.877275529201269</v>
       </c>
       <c r="G63">
-        <v>-6.076017322226465</v>
+        <v>-7.961476135936148</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-7.92999909053723</v>
       </c>
       <c r="E64">
-        <v>-14.76297678135522</v>
+        <v>-17.74774834149884</v>
       </c>
       <c r="F64">
-        <v>5.834521989263127</v>
+        <v>5.349743161061995</v>
       </c>
       <c r="G64">
-        <v>-6.69348743894745</v>
+        <v>-8.707888416278632</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-7.813716088579747</v>
       </c>
       <c r="E65">
-        <v>-15.37629971553207</v>
+        <v>-17.41420811693789</v>
       </c>
       <c r="F65">
-        <v>5.792949542786231</v>
+        <v>4.838893953959957</v>
       </c>
       <c r="G65">
-        <v>-7.392318725456427</v>
+        <v>-8.826281452586516</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-7.723691825294394</v>
       </c>
       <c r="E66">
-        <v>-15.38872131973511</v>
+        <v>-16.10430625395317</v>
       </c>
       <c r="F66">
-        <v>5.348653029559911</v>
+        <v>5.122344711849892</v>
       </c>
       <c r="G66">
-        <v>-6.445637087233234</v>
+        <v>-7.730563449911785</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-7.65583896884156</v>
       </c>
       <c r="E67">
-        <v>-15.78293856752484</v>
+        <v>-16.08115669482596</v>
       </c>
       <c r="F67">
-        <v>5.48920709699732</v>
+        <v>4.805550509262471</v>
       </c>
       <c r="G67">
-        <v>-7.037907422377684</v>
+        <v>-7.93014375126501</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-7.617025306450751</v>
       </c>
       <c r="E68">
-        <v>-15.75446805143861</v>
+        <v>-15.62749869721155</v>
       </c>
       <c r="F68">
-        <v>5.117720765007465</v>
+        <v>4.744743371692571</v>
       </c>
       <c r="G68">
-        <v>-6.275344969519614</v>
+        <v>-8.574526447216561</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-7.60695060502356</v>
       </c>
       <c r="E69">
-        <v>-13.7993944965811</v>
+        <v>-15.98580967459446</v>
       </c>
       <c r="F69">
-        <v>4.752013124019539</v>
+        <v>4.309225896201119</v>
       </c>
       <c r="G69">
-        <v>-7.155552340170015</v>
+        <v>-8.654056695374381</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-7.624275834087466</v>
       </c>
       <c r="E70">
-        <v>-15.17176213002762</v>
+        <v>-16.12940758537769</v>
       </c>
       <c r="F70">
-        <v>4.776173287689589</v>
+        <v>4.612186363161788</v>
       </c>
       <c r="G70">
-        <v>-6.275892933520041</v>
+        <v>-6.460996485352995</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-7.666776003195253</v>
       </c>
       <c r="E71">
-        <v>-13.97052100085695</v>
+        <v>-14.86900194329681</v>
       </c>
       <c r="F71">
-        <v>4.636543678273704</v>
+        <v>4.645940678091062</v>
       </c>
       <c r="G71">
-        <v>-5.276600188812711</v>
+        <v>-7.233661819392596</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-7.731645975681937</v>
       </c>
       <c r="E72">
-        <v>-13.59529164458139</v>
+        <v>-16.05527646587213</v>
       </c>
       <c r="F72">
-        <v>4.65170114501013</v>
+        <v>4.355495185851888</v>
       </c>
       <c r="G72">
-        <v>-5.907713624777868</v>
+        <v>-8.380222350130923</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-7.813762661470157</v>
       </c>
       <c r="E73">
-        <v>-13.88731481944002</v>
+        <v>-14.56755048555421</v>
       </c>
       <c r="F73">
-        <v>4.39029324370869</v>
+        <v>4.700245131548987</v>
       </c>
       <c r="G73">
-        <v>-5.895852008840476</v>
+        <v>-7.229110765089646</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-7.907337468414073</v>
       </c>
       <c r="E74">
-        <v>-13.4265063613675</v>
+        <v>-14.83191826964799</v>
       </c>
       <c r="F74">
-        <v>4.652889023865744</v>
+        <v>4.068636524466837</v>
       </c>
       <c r="G74">
-        <v>-5.289403515337665</v>
+        <v>-8.681310521647129</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-8.014991990982764</v>
       </c>
       <c r="E75">
-        <v>-13.62576827465301</v>
+        <v>-14.80496026388033</v>
       </c>
       <c r="F75">
-        <v>4.081489473088673</v>
+        <v>3.989984696305829</v>
       </c>
       <c r="G75">
-        <v>-5.525835216025014</v>
+        <v>-8.291179840672271</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-8.13487712249893</v>
       </c>
       <c r="E76">
-        <v>-13.25568326485016</v>
+        <v>-14.74026648420675</v>
       </c>
       <c r="F76">
-        <v>3.87186281813623</v>
+        <v>3.676460888224661</v>
       </c>
       <c r="G76">
-        <v>-5.449323691701881</v>
+        <v>-8.02781915464656</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-8.265909707726799</v>
       </c>
       <c r="E77">
-        <v>-14.10939118477617</v>
+        <v>-14.50604475158203</v>
       </c>
       <c r="F77">
-        <v>3.623567972821107</v>
+        <v>3.514173773607404</v>
       </c>
       <c r="G77">
-        <v>-5.779240675839369</v>
+        <v>-7.883205876857153</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-8.407667198071271</v>
       </c>
       <c r="E78">
-        <v>-14.52088003243115</v>
+        <v>-17.05011427824719</v>
       </c>
       <c r="F78">
-        <v>3.963152219394347</v>
+        <v>3.66409501963567</v>
       </c>
       <c r="G78">
-        <v>-5.441452041180773</v>
+        <v>-7.010650314883376</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-8.560303507925624</v>
       </c>
       <c r="E79">
-        <v>-14.50265292455028</v>
+        <v>-17.1312418900946</v>
       </c>
       <c r="F79">
-        <v>4.230675128863253</v>
+        <v>3.705788407753375</v>
       </c>
       <c r="G79">
-        <v>-4.221444647055836</v>
+        <v>-7.628940736994223</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-8.719996689324146</v>
       </c>
       <c r="E80">
-        <v>-14.60782220490442</v>
+        <v>-17.17947013827629</v>
       </c>
       <c r="F80">
-        <v>4.065543400584783</v>
+        <v>3.659509177693772</v>
       </c>
       <c r="G80">
-        <v>-4.752211765290054</v>
+        <v>-6.455280597396443</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-8.887618527024571</v>
       </c>
       <c r="E81">
-        <v>-15.05015901749965</v>
+        <v>-16.71857111072362</v>
       </c>
       <c r="F81">
-        <v>3.82087349102431</v>
+        <v>3.183878839089157</v>
       </c>
       <c r="G81">
-        <v>-4.611342361299974</v>
+        <v>-6.547433704893447</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-9.067107420092388</v>
       </c>
       <c r="E82">
-        <v>-16.72470719300401</v>
+        <v>-19.57036856010601</v>
       </c>
       <c r="F82">
-        <v>3.962318881787131</v>
+        <v>3.19467412308244</v>
       </c>
       <c r="G82">
-        <v>-4.850251384264703</v>
+        <v>-6.849033746972927</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-9.258936077761973</v>
       </c>
       <c r="E83">
-        <v>-16.35203642454278</v>
+        <v>-18.62823765670622</v>
       </c>
       <c r="F83">
-        <v>3.599701051211647</v>
+        <v>3.502280074438009</v>
       </c>
       <c r="G83">
-        <v>-4.812264682271012</v>
+        <v>-6.581000601446567</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-9.46344291269773</v>
       </c>
       <c r="E84">
-        <v>-17.89017790598809</v>
+        <v>-19.33546302790613</v>
       </c>
       <c r="F84">
-        <v>3.231115661866396</v>
+        <v>3.012900493681728</v>
       </c>
       <c r="G84">
-        <v>-3.828088525288045</v>
+        <v>-6.296295569176667</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-9.680557302194893</v>
       </c>
       <c r="E85">
-        <v>-18.15728541685652</v>
+        <v>-21.3305411221474</v>
       </c>
       <c r="F85">
-        <v>3.241465284196973</v>
+        <v>3.380014702519607</v>
       </c>
       <c r="G85">
-        <v>-3.646902751997067</v>
+        <v>-5.202841609377954</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-9.909630612081269</v>
       </c>
       <c r="E86">
-        <v>-19.55511665964818</v>
+        <v>-22.03675664364359</v>
       </c>
       <c r="F86">
-        <v>3.473984700693183</v>
+        <v>3.126458067461901</v>
       </c>
       <c r="G86">
-        <v>-4.024696039908413</v>
+        <v>-6.10666393159168</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-10.14257333037864</v>
       </c>
       <c r="E87">
-        <v>-20.95075159254611</v>
+        <v>-22.95931548238223</v>
       </c>
       <c r="F87">
-        <v>3.371003721911954</v>
+        <v>3.243728383941422</v>
       </c>
       <c r="G87">
-        <v>-3.942176598909938</v>
+        <v>-5.162354616555966</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-10.38320721656723</v>
       </c>
       <c r="E88">
-        <v>-21.66710636734548</v>
+        <v>-23.91648091948748</v>
       </c>
       <c r="F88">
-        <v>3.043210456950162</v>
+        <v>3.283596050303356</v>
       </c>
       <c r="G88">
-        <v>-2.898045961592797</v>
+        <v>-5.880404017738609</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-10.63248522618184</v>
       </c>
       <c r="E89">
-        <v>-23.4895816747844</v>
+        <v>-26.60976366470538</v>
       </c>
       <c r="F89">
-        <v>2.932055148638108</v>
+        <v>2.293812975394339</v>
       </c>
       <c r="G89">
-        <v>-3.805244660791191</v>
+        <v>-5.639119390364843</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-10.88971621096897</v>
       </c>
       <c r="E90">
-        <v>-25.3469986876665</v>
+        <v>-28.48381829109167</v>
       </c>
       <c r="F90">
-        <v>2.629768972743317</v>
+        <v>2.924379496283767</v>
       </c>
       <c r="G90">
-        <v>-3.418890665831254</v>
+        <v>-4.625363021023481</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-11.15408994017941</v>
       </c>
       <c r="E91">
-        <v>-26.70788211102958</v>
+        <v>-29.38766547523061</v>
       </c>
       <c r="F91">
-        <v>2.806415007920701</v>
+        <v>2.613660540228478</v>
       </c>
       <c r="G91">
-        <v>-3.727122056682371</v>
+        <v>-5.002001318945902</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-11.4244519939771</v>
       </c>
       <c r="E92">
-        <v>-28.46953548407147</v>
+        <v>-29.26612576133875</v>
       </c>
       <c r="F92">
-        <v>2.49627259557776</v>
+        <v>1.993158683283064</v>
       </c>
       <c r="G92">
-        <v>-3.038685680073716</v>
+        <v>-5.239610978173092</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-11.6984127530167</v>
       </c>
       <c r="E93">
-        <v>-30.49797258209026</v>
+        <v>-32.44853124836212</v>
       </c>
       <c r="F93">
-        <v>2.979331733050681</v>
+        <v>1.696992485760157</v>
       </c>
       <c r="G93">
-        <v>-3.016340561253898</v>
+        <v>-6.12036631282392</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-11.96577507962442</v>
       </c>
       <c r="E94">
-        <v>-32.22397780774377</v>
+        <v>-33.50655259432921</v>
       </c>
       <c r="F94">
-        <v>2.395695538999456</v>
+        <v>1.671308126068955</v>
       </c>
       <c r="G94">
-        <v>-2.844335645886246</v>
+        <v>-4.606633808362171</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-12.23271998458532</v>
       </c>
       <c r="E95">
-        <v>-34.52801330539536</v>
+        <v>-36.40557297066358</v>
       </c>
       <c r="F95">
-        <v>2.209133946010562</v>
+        <v>1.555648155820477</v>
       </c>
       <c r="G95">
-        <v>-3.58058270183757</v>
+        <v>-4.970645965723849</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-12.49843127206649</v>
       </c>
       <c r="E96">
-        <v>-36.4202859827145</v>
+        <v>-36.51306082970965</v>
       </c>
       <c r="F96">
-        <v>1.800089435977777</v>
+        <v>1.362158097874568</v>
       </c>
       <c r="G96">
-        <v>-3.450328049592294</v>
+        <v>-5.634148339702284</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-12.75907896334365</v>
       </c>
       <c r="E97">
-        <v>-38.5015115022407</v>
+        <v>-40.22660424038167</v>
       </c>
       <c r="F97">
-        <v>1.942732646005047</v>
+        <v>0.953426710720042</v>
       </c>
       <c r="G97">
-        <v>-3.226007337680855</v>
+        <v>-6.195844252355827</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-13.01521066950301</v>
       </c>
       <c r="E98">
-        <v>-41.12398023516365</v>
+        <v>-40.63991579882474</v>
       </c>
       <c r="F98">
-        <v>1.807269724625244</v>
+        <v>1.303095502054964</v>
       </c>
       <c r="G98">
-        <v>-3.926098613268658</v>
+        <v>-7.359273543131259</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-13.25855486851946</v>
       </c>
       <c r="E99">
-        <v>-43.28213320689515</v>
+        <v>-43.91717470241278</v>
       </c>
       <c r="F99">
-        <v>1.788306738040357</v>
+        <v>1.233264129998966</v>
       </c>
       <c r="G99">
-        <v>-3.962530016243173</v>
+        <v>-6.789738792172201</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-13.4900189654842</v>
       </c>
       <c r="E100">
-        <v>-45.87603406154071</v>
+        <v>-46.34998415118349</v>
       </c>
       <c r="F100">
-        <v>1.770998829526264</v>
+        <v>0.4945724687569231</v>
       </c>
       <c r="G100">
-        <v>-4.731487569920602</v>
+        <v>-5.879603399678105</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-13.69157117234029</v>
       </c>
       <c r="E101">
-        <v>-47.44547861956404</v>
+        <v>-49.09831502643863</v>
       </c>
       <c r="F101">
-        <v>1.493726035726408</v>
+        <v>0.7291429229424646</v>
       </c>
       <c r="G101">
-        <v>-4.150698229012649</v>
+        <v>-6.517840367648815</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-13.88661226947187</v>
       </c>
       <c r="E102">
-        <v>-49.6083898853591</v>
+        <v>-50.43961279971853</v>
       </c>
       <c r="F102">
-        <v>1.484102063240684</v>
+        <v>1.17429596806328</v>
       </c>
       <c r="G102">
-        <v>-4.624847869238648</v>
+        <v>-6.114128710639416</v>
       </c>
     </row>
   </sheetData>
